--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,31 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>StreetTRACKS Gold Shares</t>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>Newmont Corporation</t>
   </si>
   <si>
     <t>Gold Feb 26</t>
   </si>
   <si>
-    <t>Newmont Corporation</t>
+    <t>SPDR Gold Shares</t>
+  </si>
+  <si>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
   <si>
     <t>GLD</t>
   </si>
   <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>386.44</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E2">
-        <v>68.8</v>
+        <v>62.3</v>
       </c>
       <c r="F2">
-        <v>-0.37</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="I2">
+        <v>66</v>
+      </c>
+      <c r="J2">
         <v>80</v>
       </c>
-      <c r="J2">
-        <v>93</v>
-      </c>
       <c r="K2">
-        <v>62.7</v>
+        <v>58.8</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,40 +554,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>4212.9</v>
+        <v>4235</v>
       </c>
       <c r="E3">
-        <v>69.2</v>
+        <v>73.3</v>
       </c>
       <c r="F3">
-        <v>-0.13</v>
+        <v>1.16</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I3">
         <v>73</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>59.9</v>
+        <v>58.6</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O3" t="s">
         <v>24</v>
-      </c>
-      <c r="N3">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>89.76000000000001</v>
+        <v>386.8</v>
       </c>
       <c r="E4">
-        <v>54.9</v>
+        <v>76.8</v>
       </c>
       <c r="F4">
-        <v>-1.07</v>
+        <v>-0.11</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H4">
+        <v>80</v>
+      </c>
+      <c r="I4">
         <v>76</v>
       </c>
-      <c r="I4">
-        <v>66</v>
-      </c>
       <c r="J4">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>48.11568981226033</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>52.28493729186943</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -64,22 +64,22 @@
     <t>2025-12-10</t>
   </si>
   <si>
+    <t>SPDR Gold Shares</t>
+  </si>
+  <si>
+    <t>Gold Feb 26</t>
+  </si>
+  <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
-    <t>Gold Feb 26</t>
-  </si>
-  <si>
-    <t>SPDR Gold Shares</t>
+    <t>GLD</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
   <si>
     <t>NEM</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>GLD</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -507,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>92.65000000000001</v>
+        <v>387.4</v>
       </c>
       <c r="E2">
-        <v>62.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>0.04</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>58.8</v>
+        <v>59.3</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,13 +554,13 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>4235</v>
+        <v>4235.8</v>
       </c>
       <c r="E3">
         <v>73.3</v>
       </c>
       <c r="F3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G3">
         <v>50</v>
@@ -575,7 +575,7 @@
         <v>73</v>
       </c>
       <c r="K3">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -601,28 +601,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>386.8</v>
+        <v>94.09</v>
       </c>
       <c r="E4">
-        <v>76.8</v>
+        <v>64.3</v>
       </c>
       <c r="F4">
-        <v>-0.11</v>
+        <v>3.99</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I4">
+        <v>63</v>
+      </c>
+      <c r="J4">
         <v>76</v>
       </c>
-      <c r="J4">
-        <v>80</v>
-      </c>
       <c r="K4">
-        <v>56.8</v>
+        <v>57.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>Newmont Corporation</t>
   </si>
   <si>
     <t>SPDR Gold Shares</t>
@@ -70,7 +73,7 @@
     <t>Gold Feb 26</t>
   </si>
   <si>
-    <t>Newmont Corporation</t>
+    <t>NEM</t>
   </si>
   <si>
     <t>GLD</t>
@@ -79,10 +82,10 @@
     <t>GC=F</t>
   </si>
   <si>
-    <t>NEM</t>
-  </si>
-  <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>387.4</v>
+        <v>98.14</v>
       </c>
       <c r="E2">
-        <v>77.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F2">
-        <v>0.04</v>
+        <v>9.34</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>59.3</v>
+        <v>61.2</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,40 +557,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>4235.8</v>
+        <v>395.44</v>
       </c>
       <c r="E3">
-        <v>73.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F3">
-        <v>1.18</v>
+        <v>2.33</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>58.1</v>
+        <v>59.6</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,16 +604,16 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>94.09</v>
+        <v>4328.3</v>
       </c>
       <c r="E4">
-        <v>64.3</v>
+        <v>79.3</v>
       </c>
       <c r="F4">
-        <v>3.99</v>
+        <v>2.74</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>60</v>
@@ -619,22 +622,22 @@
         <v>63</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>57.1</v>
+        <v>51.4</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>Gold Feb 26</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
@@ -70,16 +73,13 @@
     <t>SPDR Gold Shares</t>
   </si>
   <si>
-    <t>Gold Feb 26</t>
+    <t>GC=F</t>
   </si>
   <si>
     <t>NEM</t>
   </si>
   <si>
     <t>GLD</t>
-  </si>
-  <si>
-    <t>GC=F</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -510,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>98.14</v>
+        <v>4435.3</v>
       </c>
       <c r="E2">
-        <v>78.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F2">
-        <v>9.34</v>
+        <v>1.69</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>61.2</v>
+        <v>65</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -557,37 +557,37 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>395.44</v>
+        <v>105.78</v>
       </c>
       <c r="E3">
-        <v>84.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F3">
-        <v>2.33</v>
+        <v>6.48</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>59.6</v>
+        <v>62.6</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,28 +604,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4328.3</v>
+        <v>416.74</v>
       </c>
       <c r="E4">
-        <v>79.3</v>
+        <v>90.7</v>
       </c>
       <c r="F4">
-        <v>2.74</v>
+        <v>4.56</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K4">
-        <v>51.4</v>
+        <v>56.8</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,31 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
   </si>
   <si>
     <t>Gold Feb 26</t>
   </si>
   <si>
+    <t>SPDR Gold Shares</t>
+  </si>
+  <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
-    <t>SPDR Gold Shares</t>
-  </si>
-  <si>
     <t>GC=F</t>
   </si>
   <si>
+    <t>GLD</t>
+  </si>
+  <si>
     <t>NEM</t>
   </si>
   <si>
-    <t>GLD</t>
-  </si>
-  <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4435.3</v>
+        <v>4329.6</v>
       </c>
       <c r="E2">
-        <v>75.8</v>
+        <v>53.9</v>
       </c>
       <c r="F2">
-        <v>1.69</v>
+        <v>-3.37</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K2">
-        <v>65</v>
+        <v>56.5</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>105.78</v>
+        <v>398.28</v>
       </c>
       <c r="E3">
-        <v>82.5</v>
+        <v>54.9</v>
       </c>
       <c r="F3">
-        <v>6.48</v>
+        <v>-3.31</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I3">
         <v>80</v>
       </c>
       <c r="J3">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>62.6</v>
+        <v>56.5</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,10 +584,10 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>416.74</v>
+        <v>101.22</v>
       </c>
       <c r="E4">
-        <v>90.7</v>
+        <v>53.6</v>
       </c>
       <c r="F4">
-        <v>4.56</v>
+        <v>-3.35</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I4">
         <v>73</v>
       </c>
       <c r="J4">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K4">
-        <v>56.8</v>
+        <v>53.7</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>41.50472307187444</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>51.940834218365</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
   </si>
   <si>
     <t>Gold Feb 26</t>
@@ -507,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4329.6</v>
+        <v>4480.5</v>
       </c>
       <c r="E2">
-        <v>53.9</v>
+        <v>62.1</v>
       </c>
       <c r="F2">
-        <v>-3.37</v>
+        <v>3.59</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J2">
         <v>76</v>
       </c>
       <c r="K2">
-        <v>56.5</v>
+        <v>54.9</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>398.28</v>
+        <v>413.18</v>
       </c>
       <c r="E3">
-        <v>54.9</v>
+        <v>63.6</v>
       </c>
       <c r="F3">
-        <v>-3.31</v>
+        <v>3.66</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I3">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>56.5</v>
+        <v>53.7</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -601,28 +601,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>101.22</v>
+        <v>109.2</v>
       </c>
       <c r="E4">
-        <v>53.6</v>
+        <v>65.8</v>
       </c>
       <c r="F4">
-        <v>-3.35</v>
+        <v>9.41</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>53.7</v>
+        <v>52.7</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -64,22 +64,22 @@
     <t>2026-01-07</t>
   </si>
   <si>
+    <t>SPDR Gold Shares</t>
+  </si>
+  <si>
+    <t>Newmont Corporation</t>
+  </si>
+  <si>
     <t>Gold Feb 26</t>
   </si>
   <si>
-    <t>SPDR Gold Shares</t>
-  </si>
-  <si>
-    <t>Newmont Corporation</t>
+    <t>GLD</t>
+  </si>
+  <si>
+    <t>NEM</t>
   </si>
   <si>
     <t>GC=F</t>
-  </si>
-  <si>
-    <t>GLD</t>
-  </si>
-  <si>
-    <t>NEM</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -507,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4480.5</v>
+        <v>413.18</v>
       </c>
       <c r="E2">
-        <v>62.1</v>
+        <v>63.6</v>
       </c>
       <c r="F2">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>54.9</v>
+        <v>53.8</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>413.18</v>
+        <v>109.2</v>
       </c>
       <c r="E3">
-        <v>63.6</v>
+        <v>65.8</v>
       </c>
       <c r="F3">
-        <v>3.66</v>
+        <v>9.41</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>53.7</v>
+        <v>52.8</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -601,28 +601,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>109.2</v>
+        <v>4476.7</v>
       </c>
       <c r="E4">
-        <v>65.8</v>
+        <v>61.9</v>
       </c>
       <c r="F4">
-        <v>9.41</v>
+        <v>2.44</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I4">
         <v>53</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>52.7</v>
+        <v>49.8</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,25 +61,25 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>Newmont Corporation</t>
+  </si>
+  <si>
+    <t>Gold Feb 26</t>
   </si>
   <si>
     <t>SPDR Gold Shares</t>
   </si>
   <si>
-    <t>Newmont Corporation</t>
-  </si>
-  <si>
-    <t>Gold Feb 26</t>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
   <si>
     <t>GLD</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>GC=F</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -507,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>413.18</v>
+        <v>108.01</v>
       </c>
       <c r="E2">
-        <v>63.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F2">
-        <v>3.66</v>
+        <v>6.04</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>53.8</v>
+        <v>57.5</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>109.2</v>
+        <v>4441.6</v>
       </c>
       <c r="E3">
-        <v>65.8</v>
+        <v>56.6</v>
       </c>
       <c r="F3">
-        <v>9.41</v>
+        <v>2.68</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>52.8</v>
+        <v>56.1</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -601,28 +601,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4476.7</v>
+        <v>409.23</v>
       </c>
       <c r="E4">
-        <v>61.9</v>
+        <v>59.9</v>
       </c>
       <c r="F4">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>49.8</v>
+        <v>52.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,28 +61,31 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
+    <t>SPDR Gold Shares</t>
+  </si>
+  <si>
     <t>Gold Feb 26</t>
   </si>
   <si>
-    <t>SPDR Gold Shares</t>
-  </si>
-  <si>
     <t>NEM</t>
   </si>
   <si>
+    <t>GLD</t>
+  </si>
+  <si>
     <t>GC=F</t>
   </si>
   <si>
-    <t>GLD</t>
-  </si>
-  <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -507,13 +510,13 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>108.01</v>
+        <v>108.99</v>
       </c>
       <c r="E2">
-        <v>66.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F2">
-        <v>6.04</v>
+        <v>7.68</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -522,13 +525,13 @@
         <v>63</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>57.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,40 +557,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>4441.6</v>
+        <v>414.47</v>
       </c>
       <c r="E3">
-        <v>56.6</v>
+        <v>61.6</v>
       </c>
       <c r="F3">
-        <v>2.68</v>
+        <v>4.06</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
         <v>53</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>56.1</v>
+        <v>58.3</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>409.23</v>
+        <v>4500.9</v>
       </c>
       <c r="E4">
-        <v>59.9</v>
+        <v>60.7</v>
       </c>
       <c r="F4">
-        <v>2.59</v>
+        <v>4.32</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="I4">
         <v>60</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>52.1</v>
+        <v>54.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,28 +604,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4500.9</v>
+        <v>4586.5</v>
       </c>
       <c r="E4">
-        <v>60.7</v>
+        <v>63.8</v>
       </c>
       <c r="F4">
-        <v>4.32</v>
+        <v>3.37</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -531,7 +531,7 @@
         <v>83</v>
       </c>
       <c r="K2">
-        <v>65.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -578,7 +578,7 @@
         <v>66</v>
       </c>
       <c r="K3">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,13 +604,13 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4586.5</v>
+        <v>4592.6</v>
       </c>
       <c r="E4">
-        <v>63.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F4">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -625,7 +625,7 @@
         <v>80</v>
       </c>
       <c r="K4">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>108.99</v>
+        <v>112.96</v>
       </c>
       <c r="E2">
-        <v>65.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="F2">
-        <v>7.68</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I2">
+        <v>76</v>
+      </c>
+      <c r="J2">
         <v>80</v>
       </c>
-      <c r="J2">
-        <v>83</v>
-      </c>
       <c r="K2">
-        <v>65.2</v>
+        <v>59.8</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,40 +554,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>414.47</v>
+        <v>422.23</v>
       </c>
       <c r="E3">
-        <v>61.6</v>
+        <v>65.3</v>
       </c>
       <c r="F3">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>58.4</v>
+        <v>58.8</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O3" t="s">
         <v>24</v>
-      </c>
-      <c r="N3">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,13 +601,13 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4592.6</v>
+        <v>4608.1</v>
       </c>
       <c r="E4">
-        <v>64.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="F4">
-        <v>3.51</v>
+        <v>3.86</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -625,19 +622,19 @@
         <v>80</v>
       </c>
       <c r="K4">
-        <v>52.6</v>
+        <v>51.8</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>47.98314273412904</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>50.56766494832259</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>112.96</v>
+        <v>114.63</v>
       </c>
       <c r="E2">
-        <v>67.5</v>
+        <v>65.5</v>
       </c>
       <c r="F2">
-        <v>9.109999999999999</v>
+        <v>4.97</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K2">
-        <v>59.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,19 +557,19 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>422.23</v>
+        <v>421.63</v>
       </c>
       <c r="E3">
-        <v>65.3</v>
+        <v>59.9</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>66</v>
@@ -575,19 +578,19 @@
         <v>73</v>
       </c>
       <c r="K3">
-        <v>58.8</v>
+        <v>57.3</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4608.1</v>
+        <v>4644.1</v>
       </c>
       <c r="E4">
-        <v>64.7</v>
+        <v>60.3</v>
       </c>
       <c r="F4">
-        <v>3.86</v>
+        <v>4.38</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>51.8</v>
+        <v>53.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
@@ -510,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>114.63</v>
+        <v>114.12</v>
       </c>
       <c r="E2">
-        <v>65.5</v>
+        <v>63.9</v>
       </c>
       <c r="F2">
-        <v>4.97</v>
+        <v>4.71</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J2">
         <v>93</v>
       </c>
       <c r="K2">
-        <v>65.09999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -557,13 +557,13 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>421.63</v>
+        <v>421.29</v>
       </c>
       <c r="E3">
-        <v>59.9</v>
+        <v>53.5</v>
       </c>
       <c r="F3">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -572,13 +572,13 @@
         <v>63</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K3">
-        <v>57.3</v>
+        <v>59.3</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,28 +604,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4644.1</v>
+        <v>4588.4</v>
       </c>
       <c r="E4">
-        <v>60.3</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>4.38</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
+        <v>60</v>
+      </c>
+      <c r="H4">
         <v>50</v>
       </c>
-      <c r="H4">
-        <v>60</v>
-      </c>
       <c r="I4">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K4">
-        <v>53.1</v>
+        <v>58.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,28 +604,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4588.4</v>
+        <v>4678.1</v>
       </c>
       <c r="E4">
-        <v>54</v>
+        <v>77.7</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
         <v>60</v>
       </c>
-      <c r="H4">
-        <v>50</v>
-      </c>
       <c r="I4">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J4">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>58.1</v>
+        <v>53.5</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,37 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
+    <t>Gold Apr 26</t>
+  </si>
+  <si>
     <t>SPDR Gold Shares</t>
   </si>
   <si>
-    <t>Gold Feb 26</t>
-  </si>
-  <si>
     <t>NEM</t>
   </si>
   <si>
+    <t>GC=F</t>
+  </si>
+  <si>
     <t>GLD</t>
   </si>
   <si>
-    <t>GC=F</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>114.12</v>
+        <v>128.73</v>
       </c>
       <c r="E2">
-        <v>63.9</v>
+        <v>60.7</v>
       </c>
       <c r="F2">
-        <v>4.71</v>
+        <v>3.61</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>60.5</v>
+        <v>58.5</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>40.44495449250464</v>
+        <v>20.49503599836755</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,13 +554,13 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>421.29</v>
+        <v>5160.3</v>
       </c>
       <c r="E3">
-        <v>53.5</v>
+        <v>56.6</v>
       </c>
       <c r="F3">
-        <v>1.65</v>
+        <v>0.09</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -575,22 +572,22 @@
         <v>73</v>
       </c>
       <c r="J3">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>59.3</v>
+        <v>53.3</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>20.49503599836755</v>
+      </c>
+      <c r="O3" t="s">
         <v>24</v>
-      </c>
-      <c r="N3">
-        <v>40.44495449250464</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>4678.1</v>
+        <v>490</v>
       </c>
       <c r="E4">
-        <v>77.7</v>
+        <v>60.5</v>
       </c>
       <c r="F4">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H4">
         <v>60</v>
       </c>
       <c r="I4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>53.5</v>
+        <v>46.5</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>20.49503599836755</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>40.44495449250464</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,31 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>SPDR Gold Shares</t>
+  </si>
+  <si>
+    <t>Gold Apr 26</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
-    <t>Gold Apr 26</t>
-  </si>
-  <si>
-    <t>SPDR Gold Shares</t>
+    <t>GLD</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
   <si>
     <t>NEM</t>
   </si>
   <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>GLD</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>128.73</v>
+        <v>473.51</v>
       </c>
       <c r="E2">
-        <v>60.7</v>
+        <v>54.9</v>
       </c>
       <c r="F2">
-        <v>3.61</v>
+        <v>-2.12</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H2">
+        <v>83</v>
+      </c>
+      <c r="I2">
         <v>80</v>
       </c>
-      <c r="I2">
-        <v>86</v>
-      </c>
       <c r="J2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>58.5</v>
+        <v>45.3</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,16 +557,16 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>5160.3</v>
+        <v>5055</v>
       </c>
       <c r="E3">
-        <v>56.6</v>
+        <v>58.5</v>
       </c>
       <c r="F3">
-        <v>0.09</v>
+        <v>-4.52</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>63</v>
@@ -572,22 +575,22 @@
         <v>73</v>
       </c>
       <c r="J3">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>53.3</v>
+        <v>39.5</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>490</v>
+        <v>116.29</v>
       </c>
       <c r="E4">
-        <v>60.5</v>
+        <v>36.2</v>
       </c>
       <c r="F4">
-        <v>1.81</v>
+        <v>-10.37</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="I4">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K4">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -531,7 +531,7 @@
         <v>83</v>
       </c>
       <c r="K2">
-        <v>45.3</v>
+        <v>44</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -557,37 +557,37 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>5055</v>
+        <v>5104</v>
       </c>
       <c r="E3">
-        <v>58.5</v>
+        <v>61.4</v>
       </c>
       <c r="F3">
-        <v>-4.52</v>
+        <v>-3.6</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>63</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J3">
         <v>73</v>
       </c>
       <c r="K3">
-        <v>39.5</v>
+        <v>42.4</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -625,7 +625,7 @@
         <v>86</v>
       </c>
       <c r="K4">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,24 +61,24 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>Gold Apr 26</t>
   </si>
   <si>
     <t>SPDR Gold Shares</t>
   </si>
   <si>
-    <t>Gold Apr 26</t>
-  </si>
-  <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
+    <t>GC=F</t>
+  </si>
+  <si>
     <t>GLD</t>
   </si>
   <si>
-    <t>GC=F</t>
-  </si>
-  <si>
     <t>NEM</t>
   </si>
   <si>
@@ -88,10 +88,7 @@
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
-  </si>
-  <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>473.51</v>
+        <v>5174.4</v>
       </c>
       <c r="E2">
-        <v>54.9</v>
+        <v>65.3</v>
       </c>
       <c r="F2">
-        <v>-2.12</v>
+        <v>-2.27</v>
       </c>
       <c r="G2">
         <v>40</v>
       </c>
       <c r="H2">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>44</v>
+        <v>50.9</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,13 +554,13 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>5104</v>
+        <v>472.53</v>
       </c>
       <c r="E3">
-        <v>61.4</v>
+        <v>62.5</v>
       </c>
       <c r="F3">
-        <v>-3.6</v>
+        <v>-3.57</v>
       </c>
       <c r="G3">
         <v>40</v>
@@ -572,13 +569,13 @@
         <v>63</v>
       </c>
       <c r="I3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>42.4</v>
+        <v>49.7</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,10 +584,10 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>116.29</v>
+        <v>116.96</v>
       </c>
       <c r="E4">
-        <v>36.2</v>
+        <v>41.7</v>
       </c>
       <c r="F4">
-        <v>-10.37</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H4">
+        <v>70</v>
+      </c>
+      <c r="I4">
         <v>76</v>
       </c>
-      <c r="I4">
-        <v>83</v>
-      </c>
       <c r="J4">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K4">
-        <v>36.2</v>
+        <v>46.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>32.23518188264562</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -507,13 +507,13 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>5174.4</v>
+        <v>5184.2</v>
       </c>
       <c r="E2">
-        <v>65.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F2">
-        <v>-2.27</v>
+        <v>-2.08</v>
       </c>
       <c r="G2">
         <v>40</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,34 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>SPDR Gold Shares</t>
   </si>
   <si>
     <t>Gold Apr 26</t>
   </si>
   <si>
-    <t>SPDR Gold Shares</t>
-  </si>
-  <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
+    <t>GLD</t>
+  </si>
+  <si>
     <t>GC=F</t>
   </si>
   <si>
-    <t>GLD</t>
-  </si>
-  <si>
     <t>NEM</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>5184.2</v>
+        <v>477.86</v>
       </c>
       <c r="E2">
-        <v>65.59999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="F2">
-        <v>-2.08</v>
+        <v>2.08</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I2">
+        <v>80</v>
+      </c>
+      <c r="J2">
         <v>73</v>
       </c>
-      <c r="J2">
-        <v>70</v>
-      </c>
       <c r="K2">
-        <v>50.9</v>
+        <v>60</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,40 +557,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>472.53</v>
+        <v>5221.9</v>
       </c>
       <c r="E3">
-        <v>62.5</v>
+        <v>61.7</v>
       </c>
       <c r="F3">
-        <v>-3.57</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I3">
+        <v>76</v>
+      </c>
+      <c r="J3">
         <v>70</v>
       </c>
-      <c r="J3">
-        <v>80</v>
-      </c>
       <c r="K3">
-        <v>49.7</v>
+        <v>58.4</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>116.96</v>
+        <v>118.9</v>
       </c>
       <c r="E4">
-        <v>41.7</v>
+        <v>40.9</v>
       </c>
       <c r="F4">
-        <v>-8.960000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I4">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="J4">
         <v>93</v>
       </c>
       <c r="K4">
-        <v>46.1</v>
+        <v>47.2</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>SPDR Gold Shares</t>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -510,13 +507,13 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>477.86</v>
+        <v>476.24</v>
       </c>
       <c r="E2">
-        <v>60.6</v>
+        <v>59</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -531,7 +528,7 @@
         <v>73</v>
       </c>
       <c r="K2">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,40 +554,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>5221.9</v>
+        <v>5190.4</v>
       </c>
       <c r="E3">
-        <v>61.7</v>
+        <v>56.5</v>
       </c>
       <c r="F3">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
+        <v>66</v>
+      </c>
+      <c r="I3">
         <v>70</v>
       </c>
-      <c r="I3">
-        <v>76</v>
-      </c>
       <c r="J3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>58.4</v>
+        <v>55.5</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O3" t="s">
         <v>24</v>
-      </c>
-      <c r="N3">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>118.9</v>
+        <v>116.21</v>
       </c>
       <c r="E4">
-        <v>40.9</v>
+        <v>36.2</v>
       </c>
       <c r="F4">
-        <v>0.32</v>
+        <v>-2.65</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>66</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="J4">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K4">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>41.74287521812095</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>43.44936356612781</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,7 +554,7 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>5190.4</v>
+        <v>5190.2</v>
       </c>
       <c r="E3">
         <v>56.5</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,34 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>Newmont Corporation</t>
+  </si>
+  <si>
+    <t>Gold Jun 26</t>
   </si>
   <si>
     <t>SPDR Gold Shares</t>
   </si>
   <si>
-    <t>Gold Apr 26</t>
-  </si>
-  <si>
-    <t>Newmont Corporation</t>
+    <t>NEM</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
   <si>
     <t>GLD</t>
   </si>
   <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>476.24</v>
+        <v>114.65</v>
       </c>
       <c r="E2">
-        <v>59</v>
+        <v>54.4</v>
       </c>
       <c r="F2">
-        <v>0.9399999999999999</v>
+        <v>11.18</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I2">
         <v>80</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>59.5</v>
+        <v>70</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,28 +557,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>5190.2</v>
+        <v>4830.3</v>
       </c>
       <c r="E3">
-        <v>56.5</v>
+        <v>44.8</v>
       </c>
       <c r="F3">
-        <v>2.47</v>
+        <v>6.72</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>70</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K3">
-        <v>55.5</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,10 +587,10 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>116.21</v>
+        <v>431.81</v>
       </c>
       <c r="E4">
-        <v>36.2</v>
+        <v>39.8</v>
       </c>
       <c r="F4">
-        <v>-2.65</v>
+        <v>4.16</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I4">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J4">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>47.5</v>
+        <v>58.2</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,37 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>Gold Jun 26</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
-    <t>Gold Jun 26</t>
-  </si>
-  <si>
     <t>SPDR Gold Shares</t>
   </si>
   <si>
+    <t>GC=F</t>
+  </si>
+  <si>
     <t>NEM</t>
   </si>
   <si>
-    <t>GC=F</t>
-  </si>
-  <si>
     <t>GLD</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>114.65</v>
+        <v>4713.2</v>
       </c>
       <c r="E2">
-        <v>54.4</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>11.18</v>
+        <v>2.13</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K2">
-        <v>70</v>
+        <v>57.9</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>4830.3</v>
+        <v>115.1</v>
       </c>
       <c r="E3">
-        <v>44.8</v>
+        <v>51.7</v>
       </c>
       <c r="F3">
-        <v>6.72</v>
+        <v>6.96</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>63</v>
+        <v>56.1</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,10 +584,10 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>431.81</v>
+        <v>430.96</v>
       </c>
       <c r="E4">
-        <v>39.8</v>
+        <v>44.4</v>
       </c>
       <c r="F4">
-        <v>4.16</v>
+        <v>3.25</v>
       </c>
       <c r="G4">
         <v>30</v>
       </c>
       <c r="H4">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I4">
         <v>73</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>58.2</v>
+        <v>55.9</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/헷징_금_분석.xlsx
+++ b/DECISION/헷징_금_분석.xlsx
@@ -61,34 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>Gold Jun 26</t>
+    <t>2026-06-07</t>
   </si>
   <si>
     <t>Newmont Corporation</t>
   </si>
   <si>
+    <t>Gold Aug 26</t>
+  </si>
+  <si>
     <t>SPDR Gold Shares</t>
   </si>
   <si>
+    <t>NEM</t>
+  </si>
+  <si>
     <t>GC=F</t>
   </si>
   <si>
-    <t>NEM</t>
-  </si>
-  <si>
     <t>GLD</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>⛔ 관망하십시오.</t>
-  </si>
-  <si>
-    <t>⚪ 중립 구간</t>
+    <t>🤏 바닥권 접근 구간입니다.</t>
+  </si>
+  <si>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -507,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4713.2</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>36.8</v>
       </c>
       <c r="F2">
-        <v>2.13</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="J2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>57.9</v>
+        <v>39.9</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>115.1</v>
+        <v>4337.1</v>
       </c>
       <c r="E3">
-        <v>51.7</v>
+        <v>32.3</v>
       </c>
       <c r="F3">
-        <v>6.96</v>
+        <v>-4.9</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="J3">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K3">
-        <v>56.1</v>
+        <v>37.1</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -601,28 +601,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>430.96</v>
+        <v>396.24</v>
       </c>
       <c r="E4">
-        <v>44.4</v>
+        <v>32.7</v>
       </c>
       <c r="F4">
-        <v>3.25</v>
+        <v>-5.01</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I4">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K4">
-        <v>55.9</v>
+        <v>35.9</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>
